--- a/data_extactor/batch_10_fa/batch_0052_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0052_fa.xlsx
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | امنیت و ایمنی عمومی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | قدرت بدنی بالاتنه | تشخیص گفتار | حساسیت به مسئله | قدرت ایستا | بیان شفاهی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری حرکتی | قدرت پویا | قدرت انفجاری | زبردستی دستی | تعادل کلی بدن | استقامت بدنی</t>
+          <t>درک شفاهی | قدرت تنه | تشخیص گفتار | حساسیت به مسئله | قدرت ایستا | بیان شفاهی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | قدرت پویا | قدرت انفجاری | مهارت دستی | تعادل کلی بدن | استقامت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | موقعیت‌های درگیری</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های فوریت‌های پزشکی | دستیاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | دستیاران پرستاری | دستیاران کاردرمانی | پارامدیک‌ها | نمایندگان بیمار | دستیاران مراقبت شخصی | دستیاران فیزیوتراپی | بهیاران روان‌پزشکی | پرستاران ثبت‌نام‌شده | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های فوریت‌های پزشکی | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | کمک‌پرستاران | دستیاران کاردرمانی | پارامدیک‌ها | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | کمک‌یاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Psychiatric Aides</t>
+          <t>کمک‌یاران روان‌پزشکی (Psychiatric Aides)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب خواندن | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>روان‌شناسی | مشتری‌مداری و خدمات شخصی | درمان و مشاوره | زبان انگلیسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | بینایی نزدیک | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | قدرت بدنی بالاتنه</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | بینایی نزدیک | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | قدرت تنه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>تماس با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های درگیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | سلامت و ایمنی سایر کارکنان | پیامد خطا | محیط داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | فشار زمانی | برخورد با افراد خشن یا متجاوز فیزیکی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | سلامت و ایمنی سایر کارکنان | پیامد خطا | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | فشار زمانی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان پرستاری بالینی | پزشکان طب اورژانس | مددکاران اجتماعی حوزه سلامت | دستیاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | دستیاران پرستاری | دستیاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | پرستاران ثبت‌نام‌شده</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کمک‌پرستاران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Occupational Therapy Assistants</t>
+          <t>دستیاران کاردرمانی (Occupational Therapy Assistants)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار حسابداری | BrainTrain Captain's Log | BrainTrain IVA+Plus | BrainTrain SmartDriver | نرم‌افزار مدیریت پرونده‌های مشتری | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | Fifth Walk BillingTracker | FileMaker Pro | نرم‌افزار اسناد مالی | نرم‌افزار گرافیکی | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار آموزشی هنرهای زبان | نرم‌افزار آموزشی ریاضی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار مستندسازی بیمار | نرم‌افزار زمان‌بندی | نرم‌افزار صفحه‌خوان | SpectraSoft DocuPRO | نرم‌افزار اسکن متن | TheraClin Systems iMAPR | Visual Health Information VHI PC-Kits | نرم‌افزار مرورگر وب | dBASE | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار حسابداری | BrainTrain Captain's Log | BrainTrain IVA+Plus | BrainTrain SmartDriver | نرم‌افزار مدیریت پرونده‌های مشتری | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | Fifth Walk BillingTracker | FileMaker Pro | نرم‌افزار اسناد مالی | نرم‌افزار گرافیکی | سیستم اطلاعات آزمایشگاهی LIS | نرم‌افزار آموزشی هنرهای زبانی | نرم‌افزار آموزشی ریاضی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار مستندسازی بیمار | نرم‌افزار زمان‌بندی | نرم‌افزار صفحه‌خوان | SpectraSoft DocuPRO | نرم‌افزار اسکن متن | TheraClin Systems iMAPR | Visual Health Information VHI PC-Kits | نرم‌افزار مرورگر وب | dBASE | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | نظارت | تفکر انتقادی | نگارش | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | درمان و مشاوره | امنیت و ایمنی عمومی | جامعه‌شناسی و انسان‌شناسی | اداری | پزشکی و دندان‌پزشکی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | قدرت ایستا | روانی ایده‌ها | زبردستی انگشتان | انعطاف‌پذیری دسته‌بندی | زبردستی دستی | ثبات بازو-دست | توجه انتخابی | قدرت بدنی بالاتنه</t>
+          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | قدرت ایستا | روانی ایده‌ها | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تماس با دیگران | نزدیکی فیزیکی | فشار زمانی | فراوانی تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | محیط داخلی، کنترل‌شده از نظر دما | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | ایمیل</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | ارتباط با دیگران | نزدیکی فیزیکی | فشار زمانی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | ایمیل</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژ درمانگران | دستیاران پزشکی | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | پرتودرمانگران | درمانگران تفریحی | پرستاران ثبت‌نام‌شده | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژدرمانگران | دستیاران پزشکی | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | پرتودرمانگران | درمانگران تفریحی | پرستاران ثبت‌شده | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Occupational Therapy Aides</t>
+          <t>کمک‌یاران کاردرمانی (Occupational Therapy Aides)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب خواندن | نگارش | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | زبان انگلیسی | مشتری‌مداری و خدمات شخصی | روان‌شناسی | کامپیوتر و الکترونیک | آموزش و پرورش | پزشکی و دندان‌پزشکی | امنیت و ایمنی عمومی</t>
+          <t>درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | بینایی نزدیک | قدرت بدنی بالاتنه | زبردستی انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | بینایی نزدیک | قدرت تنه | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>تماس با دیگران | محیط داخلی، کنترل‌شده از نظر دما | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | مکالمات تلفنی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | تعیین وظایف, اولویت‌ها و اهداف</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | مکالمات تلفنی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان پرستاری بالینی | دستیاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | دستیاران پرستاری | کاردرمانگران | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | پرستاران ثبت‌نام‌شده | مشاوران توانبخشی | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کمک‌پرستاران | کاردرمانگران | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | پرستاران ثبت‌شده | مشاوران توانبخشی | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Physical Therapist Assistants</t>
+          <t>دستیاران فیزیوتراپی (Physical Therapist Assistants)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | پزشکی و دندان‌پزشکی | کامپیوتر و الکترونیک | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | استدلال قیاسی | توجه انتخابی | استدلال استقرایی | قدرت ایستا | ثبات بازو-دست | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بینایی دور | قدرت بدنی بالاتنه | هماهنگی چندعضوی | زبردستی انگشتان | زبردستی دستی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | استدلال قیاسی | توجه انتخابی | استدلال استقرایی | قدرت ایستا | ثبات دست و بازو | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بینایی دور | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | تماس با دیگران | محیط داخلی، کنترل‌شده از نظر دما | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | پیامد خطا | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم شدن یا چرخاندن بدن | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
+          <t>نزدیکی فیزیکی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | پیامد خطا | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | پزشکان طب اورژانس | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژ درمانگران | دستیاران پزشکی | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | دستیاران پزشک | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | پرتودرمانگران | درمانگران تفریحی | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | پزشکان طب اورژانس | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژدرمانگران | دستیاران پزشکی | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | فیزیوتراپیست‌ها | دستیاران پزشک | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | پرتودرمانگران | درمانگران تفریحی | درمانگران تنفسی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physical Therapist Aides</t>
+          <t>کمک‌یاران فیزیوتراپی (Physical Therapist Aides)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری روش‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار نگهداری پرونده بیمار | نرم‌افزار زمان‌بندی</t>
+          <t>Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار نگهداری سوابق بیمار | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نظارت | درک مطلب خواندن | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | کامپیوتر و الکترونیک | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک کتبی | وضوح گفتار | قدرت بدنی بالاتنه | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک کتبی | وضوح گفتار | قدرت تنه | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان برای ایستادن | مکالمات تلفنی | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | ایمیل | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | مکالمات تلفنی | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | پزشکان طب اورژانس | دستیاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژ درمانگران | دستیاران پزشکی | دستیاران پرستاری | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | جراحان ارتوپد، به جز اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | پرتودرمانگران | درمانگران تفریحی | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماساژدرمانگران | دستیاران پزشکی | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | جراحان ارتوپد، به‌جز کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | پرتودرمانگران | درمانگران تفریحی | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Massage Therapists</t>
+          <t>ماساژدرمانگران (Massage Therapists)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | امنیت و ایمنی عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت پویا | قدرت بدنی بالاتنه | درک شفاهی | بیان شفاهی | زبردستی دستی | هماهنگی چندعضوی | حساسیت به مسئله | انعطاف‌پذیری حرکتی | استقامت بدنی | زبردستی انگشتان | ثبات بازو-دست | توجه انتخابی | وضوح گفتار | استدلال قیاسی | بیان کتبی | درک کتبی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | قدرت ایستا</t>
+          <t>قدرت پویا | قدرت تنه | درک شفاهی | بیان شفاهی | مهارت دستی | هماهنگی چند عضو | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | استدلال قیاسی | بیان کتبی | درک کتبی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | محیط داخلی، کنترل‌شده از نظر دما | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان برای ایستادن | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای خم شدن یا چرخاندن بدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان برای ایستادن | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای خم کردن یا چرخاندن بدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | کایروپراکتورها | متخصصان پوست | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پزشکان طب سنتی | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | پرتودرمانگران | درمانگران تفریحی | پرستاران ثبت‌نام‌شده | درمانگران تنفسی | متخصصان مراقبت از پوست</t>
+          <t>طب‌سوزنی‌ها | کایروپراکتورها | متخصصان پوست | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پزشکان ناتوروپاتی | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | پرتودرمانگران | درمانگران تفریحی | پرستاران ثبت‌شده | درمانگران تنفسی | متخصصان مراقبت از پوست</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dental Assistants</t>
+          <t>دستیاران دندان‌پزشکی (Dental Assistants)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداره و مدیریت | اداری | کامپیوتر و الکترونیک | فروش و بازاریابی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | زبردستی انگشتان | ثبات بازو-دست | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | دقت کنترل | زبردستی دستی | اشتراک زمانی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | دقت کنترل | مهارت دستی | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تماس با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تشعشع | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، کنترل‌شده از نظر دما | اهمیت تکرار وظایف یکسان | ایمیل | صرف زمان برای انجام حرکات تکراری | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای خم شدن یا چرخاندن بدن | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای راه رفتن یا دویدن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های درگیری | آزادی در تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تابش | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | ایمیل | صرف زمان برای انجام حرکات تکراری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای خم کردن یا چرخاندن بدن | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای راه رفتن یا دویدن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان قلب | کایروپراکتورها | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتزهای دندانی | دندان‌پزشکان عمومی | متخصصان پوست | تکنسین‌های آندوسکوپی | دستیاران پزشکی | تکنسین‌های پزشکی چشم‌پزشکی | کارشناسان پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | دستیاران فیزیوتراپی | متخصصان پروتزهای دندانی | دستیاران جراحی | تکنسین‌های جراحی | کارشناسان و تکنسین‌های دامپزشکی</t>
+          <t>متخصصان قلب | کایروپراکتورها | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتز دندان | دندانپزشکان، عمومی | متخصصان پوست | تکنسین‌های آندوسکوپی | دستیاران پزشکی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | کمک‌یاران فیزیوتراپی | متخصصان پروتز دندان | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medical Assistants</t>
+          <t>دستیاران پزشکی (Medical Assistants)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار زمان‌بندی نوبت | نرم‌افزار صدور صورتحساب | نرم‌افزار حسابداری | برنامه‌های کاربردی نرم‌افزار تجاری | نرم‌افزار ورود داده‌ها | نرم‌افزار پایگاه داده | نرم‌افزار کدگذاری تشخیصی و روش کار | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری روش‌های رایج مراقبت‌های بهداشتی HCPCS | IDX Systems Patient Chart Tracking | Intuit QuickBooks | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری روش‌های پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Windows Vista Business | Microsoft Windows XP Professional | Microsoft Word | نرم‌افزار مدیریت بیمار | نرم‌افزار تشخیص الکتریکی بینایی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار صدور صورتحساب | نرم‌افزار حسابداری | برنامه‌های نرم‌افزاری تجاری | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | IDX Systems Patient Chart Tracking | Intuit QuickBooks | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Windows Vista Business | Microsoft Windows XP Professional | Microsoft Word | نرم‌افزار مدیریت بیمار | نرم‌افزار تشخیص الکتریکی بینایی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مشتری‌مداری و خدمات شخصی | پزشکی و دندان‌پزشکی | اداری | کامپیوتر و الکترونیک | آموزش و پرورش | امنیت و ایمنی عمومی | درمان و مشاوره</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | آموزش و پرورش | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | زبردستی انگشتان | ثبات بازو-دست | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>تماس با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، کنترل‌شده از نظر دما | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | نزدیکی فیزیکی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان | پیامد خطا | برخورد با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | مکالمات تلفنی | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان قلب | تکنسین‌ها و کارشناسان قلب و عروق | دستیاران دندان‌پزشک | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان طب داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان سوابق پزشکی | پرستاران متخصص | دستیاران پرستاری | تکنسین‌های پزشکی چشم‌پزشکی | کارشناسان پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | جراحان ارتوپد، به جز اطفال | پارامدیک‌ها | جراحان اطفال | دستیاران فیزیوتراپی | دستیاران پزشک | پرستاران ثبت‌نام‌شده | دستیاران جراحی</t>
+          <t>متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | دستیاران دندان‌پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان مدارک پزشکی | پرستاران متخصص | کمک‌پرستاران | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | کمک‌یاران فیزیوتراپی | دستیاران پزشک | پرستاران ثبت‌شده | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medical Equipment Preparers</t>
+          <t>آماده‌سازان تجهیزات پزشکی (Medical Equipment Preparers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب خواندن | سخن گفتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | امنیت و ایمنی عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | زبردستی دستی | زبردستی انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | ثبات بازو-دست | تشخیص گفتار | قدرت بدنی بالاتنه | انعطاف‌پذیری دسته‌بندی | درک کتبی | دقت کنترل | تجسم فضایی | انعطاف‌پذیری بستار | استدلال استقرایی | قدرت ایستا | هماهنگی چندعضوی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | مهارت دستی | مهارت انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | ثبات دست و بازو | تشخیص گفتار | قدرت تنه | انعطاف‌پذیری دسته‌بندی | درک کتبی | دقت کنترل | تجسم | انعطاف‌پذیری بستار | استدلال استقرایی | قدرت ایستا | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تماس با دیگران | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | ایمیل | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض شرایط خطرناک | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | ایمیل | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض شرایط خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان قلب و عروق | اپراتورهای سیستم و کارخانه شیمیایی | سیتوتکنسین‌ها | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | هیستوتکنسین‌ها | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های نورودیاگنوستیک | تکنسین‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | کارشناسان پزشکی چشم‌پزشکی | فلبوتومیست‌ها | تکنسین‌ها و کارشناسان رادیولوژی | دستیاران جراحی | تکنسین‌های جراحی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>دستیاران متخصص بیهوشی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | اپراتورهای کارخانه و سامانه‌های شیمیایی | سیتوتکنولوژیست‌ها | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | هیستوتکنولوژیست‌ها | تعمیرکاران تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | فلبوتومیست‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0052_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0052_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | استحکام بالاتنه | تشخیص گفتار | حساسیت به مسئله | استحکام استاتیک | بیان شفاهی | دید نزدیک | وضوح گفتار | انعطاف‌پذیری کششی | قدرت دینامیک | قدرت انفجاری | چابکی دستی | تعادل عمومی بدن | استقامت</t>
+          <t>درک شفاهی | قدرت تنه | تشخیص گفتار | حساسیت به مسئله | قدرت ایستا | بیان شفاهی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | قدرت پویا | قدرت انفجاری | مهارت دستی | تعادل کلی بدن | استقامت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | رانندگان و خدمه آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های فوریت‌های پزشکی (EMT) | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کمک‌بهیاران | کاردانی‌های کاردرمانی | تکنسین‌های پیش‌بیمارستانی (پارامدیک) | رابطان و متصدیان امور بیماران | مراقبان مراقبت‌های فردی | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | کارشناسان پرستاری | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کمک‌پرستاران | کاردان‌های کاردرمانی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | زبان انگلیسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید دور | دید نزدیک | بیان کتبی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بازشناسی | طبقه‌بندی منعطف | تمرکز شنیداری | استحکام بالاتنه</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | بینایی نزدیک | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | قدرت تنه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی سلامت روان | کارشناسان ارشد بالینی پرستاری | پزشکان طب اورژانس | مددکاران اجتماعی حوزه سلامت | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | پرستاران دوره‌دیده مراقبت اولیه | کمک‌بهیاران | کمک‌یاران کاردرمانی | کاردانی‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کاردانی‌های فیزیوتراپی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پزشکان طب اورژانس | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | کمک‌پرستاران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | زبان انگلیسی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی | اداری و سازمانی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | دید نزدیک | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | استحکام استاتیک | روانی ایده‌ها | چابکی انگشتان | طبقه‌بندی منعطف | چابکی دستی | ثبات دست و بازو | توجه انتخابی | استحکام بالاتنه</t>
+          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | قدرت ایستا | روانی ایده‌ها | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی سلامت روان | کارشناسان ارشد بالینی پرستاری | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | دستیاران پزشک | پرستاران دوره‌دیده مراقبت اولیه | کارشناسان کاردرمانی | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | رادیوتراپیست‌ها | کارشناسان تفریح‌درمانی | کارشناسان پرستاری | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کمک‌پزشکان و دستیاران مطب | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | آموزش و تدریس | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
+          <t>درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | دید نزدیک | استحکام بالاتنه | چابکی انگشتان | طبقه‌بندی منعطف | استدلال استقرایی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | بینایی نزدیک | قدرت تنه | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی سلامت روان | کارشناسان ارشد بالینی پرستاری | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | کمک‌بهیاران | کارشناسان کاردرمانی | کاردانی‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | کارشناسان تفریح‌درمانی | کارشناسان پرستاری | مشاوران توانبخشی | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کمک‌پرستاران | کاردرمانگران | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | پرستاران | مشاوران توانبخشی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | زبان انگلیسی | آموزش و تدریس | روان‌شناسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | دید نزدیک | بیان کتبی | استدلال قیاسی | توجه انتخابی | استدلال استقرایی | استحکام استاتیک | ثبات دست و بازو | مرتب‌سازی اطلاعات | روانی ایده‌ها | دید دور | استحکام بالاتنه | هماهنگی چندعضوی | چابکی انگشتان | چابکی دستی | تجسم فضایی | سرعت ادراک | طبقه‌بندی منعطف</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | استدلال قیاسی | توجه انتخابی | استدلال استقرایی | قدرت ایستا | ثبات دست و بازو | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بینایی دور | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی سلامت روان | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | دستیاران پزشک | پرستاران دوره‌دیده مراقبت اولیه | کارشناسان کاردرمانی | کمک‌یاران کاردرمانی | کاردانی‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کارشناسان فیزیوتراپی | دستیاران پزشک (PA) | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | رادیوتراپیست‌ها | کارشناسان تفریح‌درمانی | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کمک‌پزشکان و دستیاران مطب | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | فیزیوتراپیست‌ها | دستیاران پزشک | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | بیان شفاهی | درک کتبی | وضوح گفتار | استحکام بالاتنه | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک کتبی | وضوح گفتار | قدرت تنه | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی سلامت روان | پزشکان طب اورژانس | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | دستیاران پزشک | کمک‌بهیاران | کارشناسان کاردرمانی | کمک‌یاران کاردرمانی | کاردانی‌های کاردرمانی | جراحان ارتوپدی، به جز اطفال | متخصصان طب فیزیکی و توانبخشی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | رادیوتراپیست‌ها | کارشناسان تفریح‌درمانی | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کمک‌پزشکان و دستیاران مطب | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | جراحان ارتوپدی، غیر از اطفال | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AppointmentQuest Online Appointment Manager | ICS Software SammyUSA | Land Software Customer Pro-File | Massage Suite | Microsoft Excel | Microsoft Word | نرم‌افزار نوبت‌دهی | WinCity Custom Software WinCity Massage SOAP Notes</t>
+          <t>AppointmentQuest Online Appointment Manager | ICS Software SammyUSA | Land Software Customer Pro-File | Massage Suite | Microsoft Excel | Microsoft Word | نرم‌افزار زمان‌بندی | WinCity Custom Software WinCity Massage SOAP Notes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت دینامیک | استحکام بالاتنه | درک شفاهی | بیان شفاهی | چابکی دستی | هماهنگی چندعضوی | حساسیت به مسئله | انعطاف‌پذیری کششی | استقامت | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | استدلال قیاسی | بیان کتبی | درک کتبی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | استحکام استاتیک</t>
+          <t>قدرت پویا | قدرت تنه | درک شفاهی | بیان شفاهی | مهارت دستی | هماهنگی چند عضو | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | استدلال قیاسی | بیان کتبی | درک کتبی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | کایروپراکتورها | متخصصان پوست | بهیاران و کمک‌پرستاران دارای مجوز | پزشکان طب سنتی و طبیعی | پرستاران دوره‌دیده مراقبت اولیه | کارشناسان کاردرمانی | کمک‌یاران کاردرمانی | کاردانی‌های کاردرمانی | جراحان ارتوپدی، به جز اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی | رادیوتراپیست‌ها | کارشناسان تفریح‌درمانی | کارشناسان پرستاری | درمانگران تنفسی | متخصصان مراقبت از پوست</t>
+          <t>متخصصان و کارشناسان طب سوزنی | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | بهیاران و کمک‌پرستاران دارای مجوز | پزشکان طب طبیعی و نتوپاتی | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | متخصصان و تکنسین‌های مراقبت از پوست</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و امور اداری | اداری و سازمانی | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | وضوح گفتار | چابکی انگشتان | ثبات دست و بازو | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | دقت کنترل | چابکی دستی | تقسیم توجه | توجه انتخابی | طبقه‌بندی منعطف</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | دقت کنترل | مهارت دستی | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | کایروپراکتورها | کارشناسان بهداشت دهان و دندان | دندانسازان (تکنسین‌های پروتز دندانی) | دندان‌پزشکان عمومی | متخصصان پوست | تکنسین‌های آندوسکوپی | دستیاران پزشک | تکنسین‌های بینایی‌سنجی و چشم‌پزشکی | کارشناسان تکنولوژی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی، به جز اطفال | جراحان اطفال | کمک‌یاران فیزیوتراپی | متخصصان پروتزهای دندانی | دستیاران جراحی | تکنسین‌های اتاق عمل | کاردانی‌ها و تکنسین‌های دامپزشکی</t>
+          <t>متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | دندان‌پزشکان عمومی | متخصصان پوست و مو | تکنسین‌های اندوسکوپی | کمک‌پزشکان و دستیاران مطب | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | کمک‌یاران فیزیوتراپی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>دستیاران پزشک (Medical Assistants)</t>
+          <t>کمک‌پزشکان و دستیاران مطب (Medical Assistants)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | اداری و سازمانی | رایانه و الکترونیک | آموزش و تدریس | ایمنی و امنیت عمومی | درمان و مشاوره</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | آموزش و پرورش | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری بازشناسی | طبقه‌بندی منعطف | چابکی انگشتان | ثبات دست و بازو | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | دستیاران دندان‌پزشک | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص داخلی | بهیاران و کمک‌پرستاران دارای مجوز | متصدیان اسناد و مدارک پزشکی | پرستاران دوره‌دیده مراقبت اولیه | کمک‌بهیاران | تکنسین‌های بینایی‌سنجی و چشم‌پزشکی | کارشناسان تکنولوژی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | جراحان ارتوپدی، به جز اطفال | تکنسین‌های پیش‌بیمارستانی (پارامدیک) | جراحان اطفال | کمک‌یاران فیزیوتراپی | دستیاران پزشک (PA) | کارشناسان پرستاری | دستیاران جراحی</t>
+          <t>متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | دستیاران دندان‌پزشک | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | پرستاران بالینی پیشرفته | کمک‌پرستاران | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | کمک‌یاران فیزیوتراپی | دستیاران پزشک | پرستاران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | چابکی دستی | چابکی انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | سرعت ادراک | ثبات دست و بازو | تشخیص گفتار | استحکام بالاتنه | طبقه‌بندی منعطف | درک کتبی | دقت کنترل | تجسم فضایی | انعطاف‌پذیری بازشناسی | استدلال استقرایی | استحکام استاتیک | هماهنگی چندعضوی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | مهارت دستی | مهارت انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | ثبات دست و بازو | تشخیص گفتار | قدرت تنه | انعطاف‌پذیری دسته‌بندی | درک کتبی | دقت کنترل | تجسم | انعطاف‌پذیری بستار | استدلال استقرایی | قدرت ایستا | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان قلب و عروق | متصدیان اتاق کنترل صنایع شیمیایی | سیتوتکنولوژیست‌ها | تکنسین‌های فوریت‌های پزشکی (EMT) | تکنسین‌های آندوسکوپی | هیستوتکنولوژیست‌ها | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان علوم آزمایشگاهی پزشکی و بالینی | تکنسین‌های نورودیاگنوستیک | کارشناسان پزشکی هسته‌ای | تکنسین‌های بینایی‌سنجی و چشم‌پزشکی | کارشناسان تکنولوژی چشم‌پزشکی | خون‌گیرها (فلبوتومیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل | متصدیان تصفیه‌خانه آب و فاضلاب</t>
+          <t>دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های قلب و عروق | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | تعمیرکاران تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | کارشناسان و تکنسین‌های خون‌گیری | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
